--- a/Entrega_6/diseno_fundaciones.xlsx
+++ b/Entrega_6/diseno_fundaciones.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e453337d7bb58d0d/Escritorio/Semestre XI/Proyecto Civil/Proyecto_civil/Entrega_6/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_23F921EDDD238D025F2C4C550DA0B50F48423D32" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BC0AC77-D13D-4C46-A832-09D28EA33D3D}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="22932" yWindow="-792" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -292,8 +298,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -356,13 +362,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -400,7 +414,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -434,6 +448,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -468,9 +483,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -642,12 +658,34 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="438" row="4">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{FD633CC8-7C6D-43AF-89BB-2DB01780B9EF}">
+  <we:reference id="wa200009404" version="1.0.0.8" store="es-ES" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;23852c4d-888e-4e0e-b1c9-ba35cb9a57fc&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AU31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:47">
+    <row r="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -790,7 +828,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:47">
+    <row r="2" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -807,7 +845,7 @@
         <v>0.2</v>
       </c>
       <c r="F2">
-        <v>47.44232519531948</v>
+        <v>47.442325195319476</v>
       </c>
       <c r="G2">
         <v>2.85</v>
@@ -816,7 +854,7 @@
         <v>47.75</v>
       </c>
       <c r="I2">
-        <v>136.087</v>
+        <v>136.08699999999999</v>
       </c>
       <c r="J2">
         <v>1.2</v>
@@ -828,13 +866,13 @@
         <v>80</v>
       </c>
       <c r="M2">
-        <v>1175.1</v>
+        <v>1175.0999999999999</v>
       </c>
       <c r="N2">
-        <v>604.8</v>
+        <v>604.79999999999995</v>
       </c>
       <c r="O2">
-        <v>0.515</v>
+        <v>0.51500000000000001</v>
       </c>
       <c r="P2">
         <v>100</v>
@@ -846,7 +884,7 @@
         <v>70</v>
       </c>
       <c r="S2">
-        <v>7.614</v>
+        <v>7.6139999999999999</v>
       </c>
       <c r="T2" t="b">
         <v>1</v>
@@ -876,7 +914,7 @@
         <v>0</v>
       </c>
       <c r="AC2">
-        <v>301.1</v>
+        <v>301.10000000000002</v>
       </c>
       <c r="AD2">
         <v>1.502</v>
@@ -912,28 +950,28 @@
         <v>88</v>
       </c>
       <c r="AO2">
-        <v>4.401328013072724</v>
+        <v>4.4013280130727237</v>
       </c>
       <c r="AP2">
-        <v>28.95469754344357</v>
+        <v>28.954697543443569</v>
       </c>
       <c r="AQ2">
-        <v>4.401328013073892</v>
+        <v>4.4013280130738917</v>
       </c>
       <c r="AR2">
-        <v>5.233534945783825</v>
+        <v>5.2335349457838252</v>
       </c>
       <c r="AS2">
-        <v>4.401328013071556</v>
+        <v>4.4013280130715557</v>
       </c>
       <c r="AT2">
-        <v>52.67586014110331</v>
+        <v>52.675860141103307</v>
       </c>
       <c r="AU2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:47">
+    <row r="3" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -977,7 +1015,7 @@
         <v>56</v>
       </c>
       <c r="O3">
-        <v>0.079</v>
+        <v>7.9000000000000001E-2</v>
       </c>
       <c r="P3">
         <v>100</v>
@@ -989,7 +1027,7 @@
         <v>70</v>
       </c>
       <c r="S3">
-        <v>7.709</v>
+        <v>7.7089999999999996</v>
       </c>
       <c r="T3" t="b">
         <v>1</v>
@@ -1055,28 +1093,28 @@
         <v>89</v>
       </c>
       <c r="AO3">
-        <v>17.50132801306884</v>
+        <v>17.501328013068839</v>
       </c>
       <c r="AP3">
-        <v>52.67586014110356</v>
+        <v>52.675860141103563</v>
       </c>
       <c r="AQ3">
-        <v>4.401328013071556</v>
+        <v>4.4013280130715557</v>
       </c>
       <c r="AR3">
-        <v>52.67586014110331</v>
+        <v>52.675860141103307</v>
       </c>
       <c r="AS3">
-        <v>30.60132801306612</v>
+        <v>30.601328013066119</v>
       </c>
       <c r="AT3">
-        <v>52.67586014110381</v>
+        <v>52.675860141103811</v>
       </c>
       <c r="AU3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:47">
+    <row r="4" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -1102,7 +1140,7 @@
         <v>30.55</v>
       </c>
       <c r="I4">
-        <v>93.17700000000001</v>
+        <v>93.177000000000007</v>
       </c>
       <c r="J4">
         <v>1.2</v>
@@ -1117,7 +1155,7 @@
         <v>824</v>
       </c>
       <c r="N4">
-        <v>88.90000000000001</v>
+        <v>88.9</v>
       </c>
       <c r="O4">
         <v>0.108</v>
@@ -1126,13 +1164,13 @@
         <v>100</v>
       </c>
       <c r="Q4">
-        <v>9.029999999999999</v>
+        <v>9.0299999999999994</v>
       </c>
       <c r="R4">
         <v>70</v>
       </c>
       <c r="S4">
-        <v>7.751</v>
+        <v>7.7510000000000003</v>
       </c>
       <c r="T4" t="b">
         <v>1</v>
@@ -1198,28 +1236,28 @@
         <v>88</v>
       </c>
       <c r="AO4">
-        <v>30.60132801306854</v>
+        <v>30.601328013068539</v>
       </c>
       <c r="AP4">
-        <v>37.56586014109362</v>
+        <v>37.565860141093623</v>
       </c>
       <c r="AQ4">
-        <v>30.60132801306612</v>
+        <v>30.601328013066119</v>
       </c>
       <c r="AR4">
-        <v>52.67586014110381</v>
+        <v>52.675860141103811</v>
       </c>
       <c r="AS4">
-        <v>30.60132801307095</v>
+        <v>30.601328013070951</v>
       </c>
       <c r="AT4">
-        <v>22.45586014108344</v>
+        <v>22.455860141083441</v>
       </c>
       <c r="AU4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:47">
+    <row r="5" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -1236,7 +1274,7 @@
         <v>0.2</v>
       </c>
       <c r="F5">
-        <v>3.349999999998541</v>
+        <v>3.3499999999985408</v>
       </c>
       <c r="G5">
         <v>3.3</v>
@@ -1260,10 +1298,10 @@
         <v>169.9</v>
       </c>
       <c r="N5">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="O5">
-        <v>0.013</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="P5">
         <v>100</v>
@@ -1275,7 +1313,7 @@
         <v>70</v>
       </c>
       <c r="S5">
-        <v>7.784</v>
+        <v>7.7839999999999998</v>
       </c>
       <c r="T5" t="b">
         <v>1</v>
@@ -1293,7 +1331,7 @@
         <v>500.9</v>
       </c>
       <c r="Y5">
-        <v>0.139</v>
+        <v>0.13900000000000001</v>
       </c>
       <c r="Z5" t="b">
         <v>1</v>
@@ -1308,7 +1346,7 @@
         <v>42.1</v>
       </c>
       <c r="AD5">
-        <v>1.507</v>
+        <v>1.5069999999999999</v>
       </c>
       <c r="AE5" t="b">
         <v>1</v>
@@ -1341,28 +1379,28 @@
         <v>89</v>
       </c>
       <c r="AO5">
-        <v>28.92632801307168</v>
+        <v>28.926328013071679</v>
       </c>
       <c r="AP5">
-        <v>22.45586014108344</v>
+        <v>22.455860141083441</v>
       </c>
       <c r="AQ5">
-        <v>30.60132801307095</v>
+        <v>30.601328013070951</v>
       </c>
       <c r="AR5">
-        <v>22.45586014108344</v>
+        <v>22.455860141083441</v>
       </c>
       <c r="AS5">
         <v>27.25132801307241</v>
       </c>
       <c r="AT5">
-        <v>22.45586014108344</v>
+        <v>22.455860141083441</v>
       </c>
       <c r="AU5" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:47">
+    <row r="6" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>51</v>
       </c>
@@ -1379,16 +1417,16 @@
         <v>0.2</v>
       </c>
       <c r="F6">
-        <v>9.495403058547366</v>
+        <v>9.4954030585473657</v>
       </c>
       <c r="G6">
         <v>3.5</v>
       </c>
       <c r="H6">
-        <v>9.800000000000001</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="I6">
-        <v>34.3</v>
+        <v>34.299999999999997</v>
       </c>
       <c r="J6">
         <v>1.2</v>
@@ -1403,10 +1441,10 @@
         <v>285.7</v>
       </c>
       <c r="N6">
-        <v>157.3</v>
+        <v>157.30000000000001</v>
       </c>
       <c r="O6">
-        <v>0.551</v>
+        <v>0.55100000000000005</v>
       </c>
       <c r="P6">
         <v>100</v>
@@ -1418,7 +1456,7 @@
         <v>70</v>
       </c>
       <c r="S6">
-        <v>6.284</v>
+        <v>6.2839999999999998</v>
       </c>
       <c r="T6" t="b">
         <v>1</v>
@@ -1436,7 +1474,7 @@
         <v>846.3</v>
       </c>
       <c r="Y6">
-        <v>0.053</v>
+        <v>5.2999999999999999E-2</v>
       </c>
       <c r="Z6" t="b">
         <v>1</v>
@@ -1448,7 +1486,7 @@
         <v>0</v>
       </c>
       <c r="AC6">
-        <v>73.09999999999999</v>
+        <v>73.099999999999994</v>
       </c>
       <c r="AD6">
         <v>1.506</v>
@@ -1487,25 +1525,25 @@
         <v>27.25132801307609</v>
       </c>
       <c r="AP6">
-        <v>17.70815861180976</v>
+        <v>17.708158611809761</v>
       </c>
       <c r="AQ6">
         <v>27.25132801307241</v>
       </c>
       <c r="AR6">
-        <v>22.45586014108344</v>
+        <v>22.455860141083441</v>
       </c>
       <c r="AS6">
-        <v>27.25132801307977</v>
+        <v>27.251328013079771</v>
       </c>
       <c r="AT6">
-        <v>12.96045708253608</v>
+        <v>12.960457082536079</v>
       </c>
       <c r="AU6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:47">
+    <row r="7" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>52</v>
       </c>
@@ -1522,7 +1560,7 @@
         <v>0.25</v>
       </c>
       <c r="F7">
-        <v>1.282499999787149</v>
+        <v>1.2824999997871489</v>
       </c>
       <c r="G7">
         <v>1.75</v>
@@ -1546,10 +1584,10 @@
         <v>199.4</v>
       </c>
       <c r="N7">
-        <v>-16.1</v>
+        <v>-16.100000000000001</v>
       </c>
       <c r="O7">
-        <v>0.081</v>
+        <v>8.1000000000000003E-2</v>
       </c>
       <c r="P7">
         <v>100</v>
@@ -1561,7 +1599,7 @@
         <v>93</v>
       </c>
       <c r="S7">
-        <v>1.003</v>
+        <v>1.0029999999999999</v>
       </c>
       <c r="T7" t="b">
         <v>1</v>
@@ -1576,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="X7">
-        <v>138.2</v>
+        <v>138.19999999999999</v>
       </c>
       <c r="Y7">
         <v>0</v>
@@ -1630,25 +1668,25 @@
         <v>10.53257801297017</v>
       </c>
       <c r="AP7">
-        <v>31.88040504428591</v>
+        <v>31.880405044285911</v>
       </c>
       <c r="AQ7">
-        <v>9.891328013076595</v>
+        <v>9.8913280130765955</v>
       </c>
       <c r="AR7">
-        <v>31.88040504428591</v>
+        <v>31.880405044285911</v>
       </c>
       <c r="AS7">
-        <v>11.17382801286374</v>
+        <v>11.173828012863741</v>
       </c>
       <c r="AT7">
-        <v>31.88040504428591</v>
+        <v>31.880405044285911</v>
       </c>
       <c r="AU7" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:47">
+    <row r="8" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>53</v>
       </c>
@@ -1665,13 +1703,13 @@
         <v>0.25</v>
       </c>
       <c r="F8">
-        <v>3.800000000001056</v>
+        <v>3.8000000000010559</v>
       </c>
       <c r="G8">
         <v>1.8</v>
       </c>
       <c r="H8">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I8">
         <v>7.38</v>
@@ -1686,10 +1724,10 @@
         <v>81</v>
       </c>
       <c r="M8">
-        <v>531.8</v>
+        <v>531.79999999999995</v>
       </c>
       <c r="N8">
-        <v>-98.40000000000001</v>
+        <v>-98.4</v>
       </c>
       <c r="O8">
         <v>0.185</v>
@@ -1704,13 +1742,13 @@
         <v>93</v>
       </c>
       <c r="S8">
-        <v>1.015</v>
+        <v>1.0149999999999999</v>
       </c>
       <c r="T8" t="b">
         <v>1</v>
       </c>
       <c r="U8">
-        <v>0.775</v>
+        <v>0.77500000000000002</v>
       </c>
       <c r="V8">
         <v>0</v>
@@ -1746,7 +1784,7 @@
         <v>82</v>
       </c>
       <c r="AG8">
-        <v>0.775</v>
+        <v>0.77500000000000002</v>
       </c>
       <c r="AH8">
         <v>10.89</v>
@@ -1770,28 +1808,28 @@
         <v>88</v>
       </c>
       <c r="AO8">
-        <v>9.891328013075135</v>
+        <v>9.8913280130751353</v>
       </c>
       <c r="AP8">
         <v>29.98040504428538</v>
       </c>
       <c r="AQ8">
-        <v>9.891328013073675</v>
+        <v>9.8913280130736752</v>
       </c>
       <c r="AR8">
-        <v>28.08040504428485</v>
+        <v>28.080405044284849</v>
       </c>
       <c r="AS8">
-        <v>9.891328013076595</v>
+        <v>9.8913280130765955</v>
       </c>
       <c r="AT8">
-        <v>31.88040504428591</v>
+        <v>31.880405044285911</v>
       </c>
       <c r="AU8" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:47">
+    <row r="9" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>54</v>
       </c>
@@ -1808,7 +1846,7 @@
         <v>0.25</v>
       </c>
       <c r="F9">
-        <v>7.277525405395011</v>
+        <v>7.2775254053950107</v>
       </c>
       <c r="G9">
         <v>2.15</v>
@@ -1835,7 +1873,7 @@
         <v>-681.1</v>
       </c>
       <c r="O9">
-        <v>0.702</v>
+        <v>0.70199999999999996</v>
       </c>
       <c r="P9">
         <v>100</v>
@@ -1847,7 +1885,7 @@
         <v>93</v>
       </c>
       <c r="S9">
-        <v>1.007</v>
+        <v>1.0069999999999999</v>
       </c>
       <c r="T9" t="b">
         <v>1</v>
@@ -1880,7 +1918,7 @@
         <v>12.9</v>
       </c>
       <c r="AD9">
-        <v>20.283</v>
+        <v>20.283000000000001</v>
       </c>
       <c r="AE9" t="b">
         <v>1</v>
@@ -1916,25 +1954,25 @@
         <v>15.68055559725541</v>
       </c>
       <c r="AP9">
-        <v>28.27894881395189</v>
+        <v>28.278948813951889</v>
       </c>
       <c r="AQ9">
-        <v>15.51969870252299</v>
+        <v>15.519698702522991</v>
       </c>
       <c r="AR9">
         <v>24.67749258361787</v>
       </c>
       <c r="AS9">
-        <v>15.84141249198782</v>
+        <v>15.841412491987819</v>
       </c>
       <c r="AT9">
-        <v>31.88040504428591</v>
+        <v>31.880405044285911</v>
       </c>
       <c r="AU9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:47">
+    <row r="10" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>55</v>
       </c>
@@ -1951,7 +1989,7 @@
         <v>0.25</v>
       </c>
       <c r="F10">
-        <v>5.099953953965137</v>
+        <v>5.0999539539651373</v>
       </c>
       <c r="G10">
         <v>1.45</v>
@@ -1972,13 +2010,13 @@
         <v>80</v>
       </c>
       <c r="M10">
-        <v>275.1</v>
+        <v>275.10000000000002</v>
       </c>
       <c r="N10">
-        <v>152.7</v>
+        <v>152.69999999999999</v>
       </c>
       <c r="O10">
-        <v>0.555</v>
+        <v>0.55500000000000005</v>
       </c>
       <c r="P10">
         <v>100</v>
@@ -1990,7 +2028,7 @@
         <v>70</v>
       </c>
       <c r="S10">
-        <v>1.916</v>
+        <v>1.9159999999999999</v>
       </c>
       <c r="T10" t="b">
         <v>1</v>
@@ -2005,7 +2043,7 @@
         <v>0</v>
       </c>
       <c r="X10">
-        <v>647.7</v>
+        <v>647.70000000000005</v>
       </c>
       <c r="Y10">
         <v>0</v>
@@ -2023,7 +2061,7 @@
         <v>56</v>
       </c>
       <c r="AD10">
-        <v>2.126</v>
+        <v>2.1259999999999999</v>
       </c>
       <c r="AE10" t="b">
         <v>1</v>
@@ -2059,25 +2097,25 @@
         <v>19.69948869256898</v>
       </c>
       <c r="AP10">
-        <v>28.64026302813764</v>
+        <v>28.640263028137639</v>
       </c>
       <c r="AQ10">
         <v>22.24946566955154</v>
       </c>
       <c r="AR10">
-        <v>28.64026302814882</v>
+        <v>28.640263028148819</v>
       </c>
       <c r="AS10">
         <v>17.14951171558641</v>
       </c>
       <c r="AT10">
-        <v>28.64026302812646</v>
+        <v>28.640263028126459</v>
       </c>
       <c r="AU10" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:47">
+    <row r="11" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>56</v>
       </c>
@@ -2094,7 +2132,7 @@
         <v>0.25</v>
       </c>
       <c r="F11">
-        <v>4.909947961302368</v>
+        <v>4.9099479613023682</v>
       </c>
       <c r="G11">
         <v>1.75</v>
@@ -2103,7 +2141,7 @@
         <v>5.25</v>
       </c>
       <c r="I11">
-        <v>9.188000000000001</v>
+        <v>9.1880000000000006</v>
       </c>
       <c r="J11">
         <v>1.2</v>
@@ -2121,7 +2159,7 @@
         <v>-280.5</v>
       </c>
       <c r="O11">
-        <v>0.535</v>
+        <v>0.53500000000000003</v>
       </c>
       <c r="P11">
         <v>100</v>
@@ -2133,7 +2171,7 @@
         <v>93</v>
       </c>
       <c r="S11">
-        <v>1.011</v>
+        <v>1.0109999999999999</v>
       </c>
       <c r="T11" t="b">
         <v>1</v>
@@ -2199,13 +2237,13 @@
         <v>88</v>
       </c>
       <c r="AO11">
-        <v>22.24946566955155</v>
+        <v>22.249465669551551</v>
       </c>
       <c r="AP11">
-        <v>29.52543106360918</v>
+        <v>29.525431063609179</v>
       </c>
       <c r="AQ11">
-        <v>22.24946566955157</v>
+        <v>22.249465669551569</v>
       </c>
       <c r="AR11">
         <v>27.07045708295799</v>
@@ -2214,13 +2252,13 @@
         <v>22.24946566955154</v>
       </c>
       <c r="AT11">
-        <v>31.98040504426036</v>
+        <v>31.980405044260358</v>
       </c>
       <c r="AU11" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:47">
+    <row r="12" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>57</v>
       </c>
@@ -2237,7 +2275,7 @@
         <v>0.25</v>
       </c>
       <c r="F12">
-        <v>2.521175053554387</v>
+        <v>2.5211750535543871</v>
       </c>
       <c r="G12">
         <v>1.45</v>
@@ -2246,7 +2284,7 @@
         <v>2.85</v>
       </c>
       <c r="I12">
-        <v>4.132</v>
+        <v>4.1319999999999997</v>
       </c>
       <c r="J12">
         <v>1.2</v>
@@ -2264,7 +2302,7 @@
         <v>-47.4</v>
       </c>
       <c r="O12">
-        <v>0.208</v>
+        <v>0.20799999999999999</v>
       </c>
       <c r="P12">
         <v>100</v>
@@ -2306,7 +2344,7 @@
         <v>0</v>
       </c>
       <c r="AC12">
-        <v>8.300000000000001</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="AD12">
         <v>4.907</v>
@@ -2345,25 +2383,25 @@
         <v>11.15191553985087</v>
       </c>
       <c r="AP12">
-        <v>25.52483099643174</v>
+        <v>25.524830996431739</v>
       </c>
       <c r="AQ12">
-        <v>9.891328013073675</v>
+        <v>9.8913280130736752</v>
       </c>
       <c r="AR12">
-        <v>25.52483099643758</v>
+        <v>25.524830996437579</v>
       </c>
       <c r="AS12">
         <v>12.41250306662806</v>
       </c>
       <c r="AT12">
-        <v>25.5248309964259</v>
+        <v>25.524830996425901</v>
       </c>
       <c r="AU12" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:47">
+    <row r="13" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>58</v>
       </c>
@@ -2380,7 +2418,7 @@
         <v>0.25</v>
       </c>
       <c r="F13">
-        <v>5.19999999998649</v>
+        <v>5.1999999999864901</v>
       </c>
       <c r="G13">
         <v>2.5</v>
@@ -2407,13 +2445,13 @@
         <v>-430.6</v>
       </c>
       <c r="O13">
-        <v>0.541</v>
+        <v>0.54100000000000004</v>
       </c>
       <c r="P13">
         <v>100</v>
       </c>
       <c r="Q13">
-        <v>92.06999999999999</v>
+        <v>92.07</v>
       </c>
       <c r="R13">
         <v>93</v>
@@ -2485,28 +2523,28 @@
         <v>89</v>
       </c>
       <c r="AO13">
-        <v>12.49132801307672</v>
+        <v>12.491328013076719</v>
       </c>
       <c r="AP13">
-        <v>22.9104570826694</v>
+        <v>22.910457082669399</v>
       </c>
       <c r="AQ13">
-        <v>15.09132801306997</v>
+        <v>15.091328013069971</v>
       </c>
       <c r="AR13">
-        <v>22.91045708266948</v>
+        <v>22.910457082669481</v>
       </c>
       <c r="AS13">
-        <v>9.891328013083479</v>
+        <v>9.8913280130834789</v>
       </c>
       <c r="AT13">
-        <v>22.91045708266932</v>
+        <v>22.910457082669321</v>
       </c>
       <c r="AU13" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:47">
+    <row r="14" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>59</v>
       </c>
@@ -2526,7 +2564,7 @@
         <v>2.399999999748033</v>
       </c>
       <c r="G14">
-        <v>2.55</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="H14">
         <v>6.1</v>
@@ -2550,7 +2588,7 @@
         <v>32.5</v>
       </c>
       <c r="O14">
-        <v>0.031</v>
+        <v>3.1E-2</v>
       </c>
       <c r="P14">
         <v>100</v>
@@ -2568,7 +2606,7 @@
         <v>1</v>
       </c>
       <c r="U14">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="V14">
         <v>0</v>
@@ -2577,7 +2615,7 @@
         <v>0</v>
       </c>
       <c r="X14">
-        <v>526.8</v>
+        <v>526.79999999999995</v>
       </c>
       <c r="Y14">
         <v>0</v>
@@ -2595,7 +2633,7 @@
         <v>18.8</v>
       </c>
       <c r="AD14">
-        <v>17.908</v>
+        <v>17.908000000000001</v>
       </c>
       <c r="AE14" t="b">
         <v>1</v>
@@ -2604,10 +2642,10 @@
         <v>82</v>
       </c>
       <c r="AG14">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="AH14">
-        <v>17.94</v>
+        <v>17.940000000000001</v>
       </c>
       <c r="AI14" t="b">
         <v>1</v>
@@ -2631,25 +2669,25 @@
         <v>15.09132801307441</v>
       </c>
       <c r="AP14">
-        <v>22.58045708254563</v>
+        <v>22.580457082545632</v>
       </c>
       <c r="AQ14">
         <v>15.09132801307441</v>
       </c>
       <c r="AR14">
-        <v>23.78045708241964</v>
+        <v>23.780457082419641</v>
       </c>
       <c r="AS14">
         <v>15.09132801307441</v>
       </c>
       <c r="AT14">
-        <v>21.38045708267161</v>
+        <v>21.380457082671612</v>
       </c>
       <c r="AU14" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:47">
+    <row r="15" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>60</v>
       </c>
@@ -2666,7 +2704,7 @@
         <v>0.25</v>
       </c>
       <c r="F15">
-        <v>5.55813765648135</v>
+        <v>5.5581376564813496</v>
       </c>
       <c r="G15">
         <v>2.15</v>
@@ -2693,19 +2731,19 @@
         <v>-410.4</v>
       </c>
       <c r="O15">
-        <v>0.542</v>
+        <v>0.54200000000000004</v>
       </c>
       <c r="P15">
         <v>100</v>
       </c>
       <c r="Q15">
-        <v>92.54000000000001</v>
+        <v>92.54</v>
       </c>
       <c r="R15">
         <v>93</v>
       </c>
       <c r="S15">
-        <v>1.005</v>
+        <v>1.0049999999999999</v>
       </c>
       <c r="T15" t="b">
         <v>1</v>
@@ -2738,7 +2776,7 @@
         <v>43.2</v>
       </c>
       <c r="AD15">
-        <v>7.009</v>
+        <v>7.0090000000000003</v>
       </c>
       <c r="AE15" t="b">
         <v>1</v>
@@ -2771,19 +2809,19 @@
         <v>89</v>
       </c>
       <c r="AO15">
-        <v>19.64948869250476</v>
+        <v>19.649488692504761</v>
       </c>
       <c r="AP15">
         <v>23.23045708254595</v>
       </c>
       <c r="AQ15">
-        <v>17.04951171545635</v>
+        <v>17.049511715456351</v>
       </c>
       <c r="AR15">
         <v>23.23045708254595</v>
       </c>
       <c r="AS15">
-        <v>22.24946566955317</v>
+        <v>22.249465669553171</v>
       </c>
       <c r="AT15">
         <v>23.23045708254595</v>
@@ -2792,7 +2830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:47">
+    <row r="16" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>61</v>
       </c>
@@ -2809,7 +2847,7 @@
         <v>0.25</v>
       </c>
       <c r="F16">
-        <v>3.269999999945643</v>
+        <v>3.2699999999456431</v>
       </c>
       <c r="G16">
         <v>1.5</v>
@@ -2833,10 +2871,10 @@
         <v>365.8</v>
       </c>
       <c r="N16">
-        <v>-1.1</v>
+        <v>-1.1000000000000001</v>
       </c>
       <c r="O16">
-        <v>0.003</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="P16">
         <v>100</v>
@@ -2863,7 +2901,7 @@
         <v>0</v>
       </c>
       <c r="X16">
-        <v>310.9</v>
+        <v>310.89999999999998</v>
       </c>
       <c r="Y16">
         <v>0</v>
@@ -2881,7 +2919,7 @@
         <v>8.4</v>
       </c>
       <c r="AD16">
-        <v>16.697</v>
+        <v>16.696999999999999</v>
       </c>
       <c r="AE16" t="b">
         <v>1</v>
@@ -2917,25 +2955,25 @@
         <v>16.87041986432531</v>
       </c>
       <c r="AP16">
-        <v>22.14496836933868</v>
+        <v>22.144968369338681</v>
       </c>
       <c r="AQ16">
         <v>17.04951171545224</v>
       </c>
       <c r="AR16">
-        <v>20.50996836936585</v>
+        <v>20.509968369365851</v>
       </c>
       <c r="AS16">
         <v>16.69132801319839</v>
       </c>
       <c r="AT16">
-        <v>23.7799683693115</v>
+        <v>23.779968369311501</v>
       </c>
       <c r="AU16" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:47">
+    <row r="17" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>62</v>
       </c>
@@ -2952,7 +2990,7 @@
         <v>0.25</v>
       </c>
       <c r="F17">
-        <v>5.200000000008435</v>
+        <v>5.2000000000084352</v>
       </c>
       <c r="G17">
         <v>2.5</v>
@@ -2979,7 +3017,7 @@
         <v>-389.7</v>
       </c>
       <c r="O17">
-        <v>0.462</v>
+        <v>0.46200000000000002</v>
       </c>
       <c r="P17">
         <v>100</v>
@@ -3024,7 +3062,7 @@
         <v>26.3</v>
       </c>
       <c r="AD17">
-        <v>4.461</v>
+        <v>4.4610000000000003</v>
       </c>
       <c r="AE17" t="b">
         <v>1</v>
@@ -3063,7 +3101,7 @@
         <v>17.71045708266114</v>
       </c>
       <c r="AQ17">
-        <v>15.09132801307137</v>
+        <v>15.091328013071371</v>
       </c>
       <c r="AR17">
         <v>17.71045708266114</v>
@@ -3078,7 +3116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:47">
+    <row r="18" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>63</v>
       </c>
@@ -3095,7 +3133,7 @@
         <v>0.25</v>
       </c>
       <c r="F18">
-        <v>5.347632615672943</v>
+        <v>5.3476326156729428</v>
       </c>
       <c r="G18">
         <v>1.45</v>
@@ -3104,7 +3142,7 @@
         <v>5.65</v>
       </c>
       <c r="I18">
-        <v>8.192</v>
+        <v>8.1920000000000002</v>
       </c>
       <c r="J18">
         <v>1.2</v>
@@ -3125,7 +3163,7 @@
         <v>1.099</v>
       </c>
       <c r="P18">
-        <v>91.59999999999999</v>
+        <v>91.6</v>
       </c>
       <c r="Q18">
         <v>91.52</v>
@@ -3167,7 +3205,7 @@
         <v>22.5</v>
       </c>
       <c r="AD18">
-        <v>4.406</v>
+        <v>4.4059999999999997</v>
       </c>
       <c r="AE18" t="b">
         <v>1</v>
@@ -3200,19 +3238,19 @@
         <v>89</v>
       </c>
       <c r="AO18">
-        <v>20.3826443206352</v>
+        <v>20.382644320635201</v>
       </c>
       <c r="AP18">
         <v>19.46045708254109</v>
       </c>
       <c r="AQ18">
-        <v>18.82632801239999</v>
+        <v>18.826328012399991</v>
       </c>
       <c r="AR18">
         <v>19.46045708254109</v>
       </c>
       <c r="AS18">
-        <v>21.93896062887041</v>
+        <v>21.938960628870412</v>
       </c>
       <c r="AT18">
         <v>19.46045708254109</v>
@@ -3221,7 +3259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:47">
+    <row r="19" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>64</v>
       </c>
@@ -3238,7 +3276,7 @@
         <v>0.25</v>
       </c>
       <c r="F19">
-        <v>5.347298337624352</v>
+        <v>5.3472983376243519</v>
       </c>
       <c r="G19">
         <v>2</v>
@@ -3259,13 +3297,13 @@
         <v>81</v>
       </c>
       <c r="M19">
-        <v>554.8</v>
+        <v>554.79999999999995</v>
       </c>
       <c r="N19">
         <v>-463.2</v>
       </c>
       <c r="O19">
-        <v>0.835</v>
+        <v>0.83499999999999996</v>
       </c>
       <c r="P19">
         <v>100</v>
@@ -3310,7 +3348,7 @@
         <v>25.4</v>
       </c>
       <c r="AD19">
-        <v>6.204</v>
+        <v>6.2039999999999997</v>
       </c>
       <c r="AE19" t="b">
         <v>1</v>
@@ -3343,19 +3381,19 @@
         <v>89</v>
       </c>
       <c r="AO19">
-        <v>19.26497718200959</v>
+        <v>19.264977182009591</v>
       </c>
       <c r="AP19">
-        <v>15.76045708253785</v>
+        <v>15.760457082537849</v>
       </c>
       <c r="AQ19">
-        <v>16.59132801319742</v>
+        <v>16.591328013197419</v>
       </c>
       <c r="AR19">
-        <v>15.76045708253501</v>
+        <v>15.760457082535011</v>
       </c>
       <c r="AS19">
-        <v>21.93862635082177</v>
+        <v>21.938626350821771</v>
       </c>
       <c r="AT19">
         <v>15.7604570825407</v>
@@ -3364,7 +3402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:47">
+    <row r="20" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>65</v>
       </c>
@@ -3408,7 +3446,7 @@
         <v>-18.5</v>
       </c>
       <c r="O20">
-        <v>0.061</v>
+        <v>6.0999999999999999E-2</v>
       </c>
       <c r="P20">
         <v>100</v>
@@ -3420,7 +3458,7 @@
         <v>70</v>
       </c>
       <c r="S20">
-        <v>1.229</v>
+        <v>1.2290000000000001</v>
       </c>
       <c r="T20" t="b">
         <v>1</v>
@@ -3453,7 +3491,7 @@
         <v>13.7</v>
       </c>
       <c r="AD20">
-        <v>7.103</v>
+        <v>7.1029999999999998</v>
       </c>
       <c r="AE20" t="b">
         <v>1</v>
@@ -3489,16 +3527,16 @@
         <v>18.82632801240052</v>
       </c>
       <c r="AP20">
-        <v>17.61045708254085</v>
+        <v>17.610457082540851</v>
       </c>
       <c r="AQ20">
-        <v>18.82632801240105</v>
+        <v>18.826328012401049</v>
       </c>
       <c r="AR20">
         <v>15.76045708254062</v>
       </c>
       <c r="AS20">
-        <v>18.82632801239999</v>
+        <v>18.826328012399991</v>
       </c>
       <c r="AT20">
         <v>19.46045708254109</v>
@@ -3507,7 +3545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:47">
+    <row r="21" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>66</v>
       </c>
@@ -3524,7 +3562,7 @@
         <v>0.25</v>
       </c>
       <c r="F21">
-        <v>4.220000017041452</v>
+        <v>4.2200000170414516</v>
       </c>
       <c r="G21">
         <v>1.45</v>
@@ -3533,7 +3571,7 @@
         <v>4.55</v>
       </c>
       <c r="I21">
-        <v>6.598</v>
+        <v>6.5979999999999999</v>
       </c>
       <c r="J21">
         <v>1.2</v>
@@ -3551,7 +3589,7 @@
         <v>-10.3</v>
       </c>
       <c r="O21">
-        <v>0.039</v>
+        <v>3.9E-2</v>
       </c>
       <c r="P21">
         <v>100</v>
@@ -3563,7 +3601,7 @@
         <v>70</v>
       </c>
       <c r="S21">
-        <v>1.638</v>
+        <v>1.6379999999999999</v>
       </c>
       <c r="T21" t="b">
         <v>1</v>
@@ -3629,19 +3667,19 @@
         <v>88</v>
       </c>
       <c r="AO21">
-        <v>21.93856401249103</v>
+        <v>21.938564012491032</v>
       </c>
       <c r="AP21">
-        <v>15.07045708244559</v>
+        <v>15.070457082445589</v>
       </c>
       <c r="AQ21">
-        <v>21.93837338365771</v>
+        <v>21.938373383657709</v>
       </c>
       <c r="AR21">
-        <v>12.96045708253608</v>
+        <v>12.960457082536079</v>
       </c>
       <c r="AS21">
-        <v>21.93875464132435</v>
+        <v>21.938754641324351</v>
       </c>
       <c r="AT21">
         <v>17.18045708235509</v>
@@ -3650,7 +3688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:47">
+    <row r="22" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>67</v>
       </c>
@@ -3667,7 +3705,7 @@
         <v>0.25</v>
       </c>
       <c r="F22">
-        <v>5.440000000037777</v>
+        <v>5.4400000000377773</v>
       </c>
       <c r="G22">
         <v>1.55</v>
@@ -3676,7 +3714,7 @@
         <v>5.75</v>
       </c>
       <c r="I22">
-        <v>8.913</v>
+        <v>8.9130000000000003</v>
       </c>
       <c r="J22">
         <v>1.2</v>
@@ -3694,7 +3732,7 @@
         <v>-34</v>
       </c>
       <c r="O22">
-        <v>0.059</v>
+        <v>5.8999999999999997E-2</v>
       </c>
       <c r="P22">
         <v>100</v>
@@ -3739,7 +3777,7 @@
         <v>10.6</v>
       </c>
       <c r="AD22">
-        <v>17.603</v>
+        <v>17.603000000000002</v>
       </c>
       <c r="AE22" t="b">
         <v>1</v>
@@ -3775,7 +3813,7 @@
         <v>15.09132801307441</v>
       </c>
       <c r="AP22">
-        <v>17.710457082663</v>
+        <v>17.710457082663002</v>
       </c>
       <c r="AQ22">
         <v>15.09132801307441</v>
@@ -3787,13 +3825,13 @@
         <v>15.09132801307441</v>
       </c>
       <c r="AT22">
-        <v>14.99045708264411</v>
+        <v>14.990457082644109</v>
       </c>
       <c r="AU22" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:47">
+    <row r="23" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>68</v>
       </c>
@@ -3813,7 +3851,7 @@
         <v>0.9</v>
       </c>
       <c r="H23">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="I23">
         <v>0.99</v>
@@ -3831,10 +3869,10 @@
         <v>45.7</v>
       </c>
       <c r="N23">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="O23">
-        <v>0.006</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="P23">
         <v>100</v>
@@ -3915,25 +3953,25 @@
         <v>9.891</v>
       </c>
       <c r="AP23">
-        <v>47.709</v>
+        <v>47.709000000000003</v>
       </c>
       <c r="AQ23">
-        <v>9.741</v>
+        <v>9.7409999999999997</v>
       </c>
       <c r="AR23">
-        <v>47.459</v>
+        <v>47.459000000000003</v>
       </c>
       <c r="AS23">
         <v>10.041</v>
       </c>
       <c r="AT23">
-        <v>47.959</v>
+        <v>47.959000000000003</v>
       </c>
       <c r="AU23" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:47">
+    <row r="24" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>69</v>
       </c>
@@ -3953,7 +3991,7 @@
         <v>0.9</v>
       </c>
       <c r="H24">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="I24">
         <v>0.99</v>
@@ -3974,7 +4012,7 @@
         <v>1.04</v>
       </c>
       <c r="O24">
-        <v>0.023</v>
+        <v>2.3E-2</v>
       </c>
       <c r="P24">
         <v>100</v>
@@ -4055,25 +4093,25 @@
         <v>9.891</v>
       </c>
       <c r="AP24">
-        <v>42.109</v>
+        <v>42.109000000000002</v>
       </c>
       <c r="AQ24">
-        <v>9.741</v>
+        <v>9.7409999999999997</v>
       </c>
       <c r="AR24">
-        <v>41.859</v>
+        <v>41.859000000000002</v>
       </c>
       <c r="AS24">
         <v>10.041</v>
       </c>
       <c r="AT24">
-        <v>42.359</v>
+        <v>42.359000000000002</v>
       </c>
       <c r="AU24" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:47">
+    <row r="25" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>70</v>
       </c>
@@ -4093,7 +4131,7 @@
         <v>0.9</v>
       </c>
       <c r="H25">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="I25">
         <v>0.99</v>
@@ -4114,7 +4152,7 @@
         <v>1.59</v>
       </c>
       <c r="O25">
-        <v>0.036</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="P25">
         <v>100</v>
@@ -4159,7 +4197,7 @@
         <v>1.41</v>
       </c>
       <c r="AD25">
-        <v>7.801</v>
+        <v>7.8010000000000002</v>
       </c>
       <c r="AE25" t="b">
         <v>1</v>
@@ -4195,25 +4233,25 @@
         <v>9.891</v>
       </c>
       <c r="AP25">
-        <v>37.109</v>
+        <v>37.109000000000002</v>
       </c>
       <c r="AQ25">
-        <v>9.741</v>
+        <v>9.7409999999999997</v>
       </c>
       <c r="AR25">
-        <v>36.859</v>
+        <v>36.859000000000002</v>
       </c>
       <c r="AS25">
         <v>10.041</v>
       </c>
       <c r="AT25">
-        <v>37.359</v>
+        <v>37.359000000000002</v>
       </c>
       <c r="AU25" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:47">
+    <row r="26" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>71</v>
       </c>
@@ -4233,7 +4271,7 @@
         <v>0.9</v>
       </c>
       <c r="H26">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="I26">
         <v>0.99</v>
@@ -4254,7 +4292,7 @@
         <v>0.48</v>
       </c>
       <c r="O26">
-        <v>0.011</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="P26">
         <v>100</v>
@@ -4299,7 +4337,7 @@
         <v>0.46</v>
       </c>
       <c r="AD26">
-        <v>24.676</v>
+        <v>24.675999999999998</v>
       </c>
       <c r="AE26" t="b">
         <v>1</v>
@@ -4332,28 +4370,28 @@
         <v>90</v>
       </c>
       <c r="AO26">
-        <v>15.841</v>
+        <v>15.840999999999999</v>
       </c>
       <c r="AP26">
-        <v>47.709</v>
+        <v>47.709000000000003</v>
       </c>
       <c r="AQ26">
-        <v>15.691</v>
+        <v>15.691000000000001</v>
       </c>
       <c r="AR26">
-        <v>47.459</v>
+        <v>47.459000000000003</v>
       </c>
       <c r="AS26">
         <v>15.991</v>
       </c>
       <c r="AT26">
-        <v>47.959</v>
+        <v>47.959000000000003</v>
       </c>
       <c r="AU26" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:47">
+    <row r="27" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>72</v>
       </c>
@@ -4373,7 +4411,7 @@
         <v>0.9</v>
       </c>
       <c r="H27">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="I27">
         <v>0.99</v>
@@ -4394,7 +4432,7 @@
         <v>0.36</v>
       </c>
       <c r="O27">
-        <v>0.018</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="P27">
         <v>100</v>
@@ -4472,28 +4510,28 @@
         <v>90</v>
       </c>
       <c r="AO27">
-        <v>15.841</v>
+        <v>15.840999999999999</v>
       </c>
       <c r="AP27">
-        <v>42.109</v>
+        <v>42.109000000000002</v>
       </c>
       <c r="AQ27">
-        <v>15.691</v>
+        <v>15.691000000000001</v>
       </c>
       <c r="AR27">
-        <v>41.859</v>
+        <v>41.859000000000002</v>
       </c>
       <c r="AS27">
         <v>15.991</v>
       </c>
       <c r="AT27">
-        <v>42.359</v>
+        <v>42.359000000000002</v>
       </c>
       <c r="AU27" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:47">
+    <row r="28" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>73</v>
       </c>
@@ -4513,7 +4551,7 @@
         <v>0.9</v>
       </c>
       <c r="H28">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="I28">
         <v>0.99</v>
@@ -4528,13 +4566,13 @@
         <v>80</v>
       </c>
       <c r="M28">
-        <v>40.8</v>
+        <v>40.799999999999997</v>
       </c>
       <c r="N28">
         <v>0.6</v>
       </c>
       <c r="O28">
-        <v>0.015</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="P28">
         <v>100</v>
@@ -4576,10 +4614,10 @@
         <v>0</v>
       </c>
       <c r="AC28">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="AD28">
-        <v>17.946</v>
+        <v>17.946000000000002</v>
       </c>
       <c r="AE28" t="b">
         <v>1</v>
@@ -4612,28 +4650,28 @@
         <v>90</v>
       </c>
       <c r="AO28">
-        <v>15.841</v>
+        <v>15.840999999999999</v>
       </c>
       <c r="AP28">
-        <v>37.109</v>
+        <v>37.109000000000002</v>
       </c>
       <c r="AQ28">
-        <v>15.691</v>
+        <v>15.691000000000001</v>
       </c>
       <c r="AR28">
-        <v>36.859</v>
+        <v>36.859000000000002</v>
       </c>
       <c r="AS28">
         <v>15.991</v>
       </c>
       <c r="AT28">
-        <v>37.359</v>
+        <v>37.359000000000002</v>
       </c>
       <c r="AU28" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:47">
+    <row r="29" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>74</v>
       </c>
@@ -4653,7 +4691,7 @@
         <v>1.2</v>
       </c>
       <c r="H29">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="I29">
         <v>1.38</v>
@@ -4686,7 +4724,7 @@
         <v>70</v>
       </c>
       <c r="S29">
-        <v>1.019</v>
+        <v>1.0189999999999999</v>
       </c>
       <c r="T29" t="b">
         <v>1</v>
@@ -4719,7 +4757,7 @@
         <v>3.89</v>
       </c>
       <c r="AD29">
-        <v>5.378</v>
+        <v>5.3780000000000001</v>
       </c>
       <c r="AE29" t="b">
         <v>1</v>
@@ -4752,28 +4790,28 @@
         <v>90</v>
       </c>
       <c r="AO29">
-        <v>22.249</v>
+        <v>22.248999999999999</v>
       </c>
       <c r="AP29">
-        <v>47.709</v>
+        <v>47.709000000000003</v>
       </c>
       <c r="AQ29">
         <v>22.099</v>
       </c>
       <c r="AR29">
-        <v>47.459</v>
+        <v>47.459000000000003</v>
       </c>
       <c r="AS29">
-        <v>22.399</v>
+        <v>22.399000000000001</v>
       </c>
       <c r="AT29">
-        <v>47.959</v>
+        <v>47.959000000000003</v>
       </c>
       <c r="AU29" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:47">
+    <row r="30" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>75</v>
       </c>
@@ -4796,7 +4834,7 @@
         <v>1.25</v>
       </c>
       <c r="I30">
-        <v>1.563</v>
+        <v>1.5629999999999999</v>
       </c>
       <c r="J30">
         <v>1.2</v>
@@ -4814,7 +4852,7 @@
         <v>9.42</v>
       </c>
       <c r="O30">
-        <v>0.163</v>
+        <v>0.16300000000000001</v>
       </c>
       <c r="P30">
         <v>100</v>
@@ -4826,13 +4864,13 @@
         <v>70</v>
       </c>
       <c r="S30">
-        <v>1.019</v>
+        <v>1.0189999999999999</v>
       </c>
       <c r="T30" t="b">
         <v>1</v>
       </c>
       <c r="U30">
-        <v>0.475</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="V30">
         <v>0</v>
@@ -4856,7 +4894,7 @@
         <v>0</v>
       </c>
       <c r="AC30">
-        <v>4.94</v>
+        <v>4.9400000000000004</v>
       </c>
       <c r="AD30">
         <v>4.266</v>
@@ -4868,7 +4906,7 @@
         <v>85</v>
       </c>
       <c r="AG30">
-        <v>0.475</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="AH30">
         <v>3.01</v>
@@ -4892,28 +4930,28 @@
         <v>90</v>
       </c>
       <c r="AO30">
-        <v>22.249</v>
+        <v>22.248999999999999</v>
       </c>
       <c r="AP30">
-        <v>42.109</v>
+        <v>42.109000000000002</v>
       </c>
       <c r="AQ30">
         <v>22.099</v>
       </c>
       <c r="AR30">
-        <v>41.859</v>
+        <v>41.859000000000002</v>
       </c>
       <c r="AS30">
-        <v>22.399</v>
+        <v>22.399000000000001</v>
       </c>
       <c r="AT30">
-        <v>42.359</v>
+        <v>42.359000000000002</v>
       </c>
       <c r="AU30" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:47">
+    <row r="31" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>76</v>
       </c>
@@ -4954,7 +4992,7 @@
         <v>9.23</v>
       </c>
       <c r="O31">
-        <v>0.166</v>
+        <v>0.16600000000000001</v>
       </c>
       <c r="P31">
         <v>100</v>
@@ -4972,7 +5010,7 @@
         <v>1</v>
       </c>
       <c r="U31">
-        <v>0.475</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="V31">
         <v>0</v>
@@ -4999,7 +5037,7 @@
         <v>4.83</v>
       </c>
       <c r="AD31">
-        <v>4.214</v>
+        <v>4.2140000000000004</v>
       </c>
       <c r="AE31" t="b">
         <v>1</v>
@@ -5008,7 +5046,7 @@
         <v>85</v>
       </c>
       <c r="AG31">
-        <v>0.475</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="AH31">
         <v>2.94</v>
@@ -5032,22 +5070,22 @@
         <v>90</v>
       </c>
       <c r="AO31">
-        <v>22.249</v>
+        <v>22.248999999999999</v>
       </c>
       <c r="AP31">
-        <v>37.109</v>
+        <v>37.109000000000002</v>
       </c>
       <c r="AQ31">
         <v>22.099</v>
       </c>
       <c r="AR31">
-        <v>36.859</v>
+        <v>36.859000000000002</v>
       </c>
       <c r="AS31">
-        <v>22.399</v>
+        <v>22.399000000000001</v>
       </c>
       <c r="AT31">
-        <v>37.359</v>
+        <v>37.359000000000002</v>
       </c>
       <c r="AU31" t="b">
         <v>1</v>

--- a/Entrega_6/diseno_fundaciones.xlsx
+++ b/Entrega_6/diseno_fundaciones.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e453337d7bb58d0d/Escritorio/Semestre XI/Proyecto Civil/Proyecto_civil/Entrega_6/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_23F921EDDD238D025F2C4C550DA0B50F48423D32" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BC0AC77-D13D-4C46-A832-09D28EA33D3D}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_23F921ED0A2B4C15FD2C4CF79DE693BF49423D3F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A8D8CF9-92F9-4F9A-9D34-1FC8EA9C80F9}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-792" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1605" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -658,32 +658,14 @@
 </a:theme>
 </file>
 
-<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
-<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="438" row="4">
-    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </wetp:taskpane>
-</wetp:taskpanes>
-</file>
-
-<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
-<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{FD633CC8-7C6D-43AF-89BB-2DB01780B9EF}">
-  <we:reference id="wa200009404" version="1.0.0.8" store="es-ES" storeType="OMEX"/>
-  <we:alternateReferences>
-    <we:reference id="WA200009404" version="1.0.0.8" store="" storeType="OMEX"/>
-  </we:alternateReferences>
-  <we:properties>
-    <we:property name="claude.fileId" value="&quot;23852c4d-888e-4e0e-b1c9-ba35cb9a57fc&quot;"/>
-  </we:properties>
-  <we:bindings/>
-  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</we:webextension>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AU31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="11.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -872,19 +854,19 @@
         <v>604.79999999999995</v>
       </c>
       <c r="O2">
-        <v>0.51500000000000001</v>
+        <v>1.325</v>
       </c>
       <c r="P2">
-        <v>100</v>
+        <v>67.5</v>
       </c>
       <c r="Q2">
-        <v>9.19</v>
+        <v>33.28</v>
       </c>
       <c r="R2">
         <v>70</v>
       </c>
       <c r="S2">
-        <v>7.6139999999999999</v>
+        <v>2.1030000000000002</v>
       </c>
       <c r="T2" t="b">
         <v>1</v>
@@ -896,13 +878,13 @@
         <v>1.5</v>
       </c>
       <c r="W2">
-        <v>461.7</v>
+        <v>55.2</v>
       </c>
       <c r="X2">
         <v>4123.7</v>
       </c>
       <c r="Y2">
-        <v>0.112</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="Z2" t="b">
         <v>1</v>
@@ -929,7 +911,7 @@
         <v>2.65</v>
       </c>
       <c r="AH2">
-        <v>6.74</v>
+        <v>3.73</v>
       </c>
       <c r="AI2" t="b">
         <v>0</v>
@@ -1015,19 +997,19 @@
         <v>56</v>
       </c>
       <c r="O3">
-        <v>7.9000000000000001E-2</v>
+        <v>1.4</v>
       </c>
       <c r="P3">
-        <v>100</v>
+        <v>67.7</v>
       </c>
       <c r="Q3">
-        <v>9.08</v>
+        <v>34.06</v>
       </c>
       <c r="R3">
         <v>70</v>
       </c>
       <c r="S3">
-        <v>7.7089999999999996</v>
+        <v>2.0550000000000002</v>
       </c>
       <c r="T3" t="b">
         <v>1</v>
@@ -1039,13 +1021,13 @@
         <v>1.65</v>
       </c>
       <c r="W3">
-        <v>275</v>
+        <v>51.9</v>
       </c>
       <c r="X3">
         <v>2288.5</v>
       </c>
       <c r="Y3">
-        <v>0.12</v>
+        <v>2.3E-2</v>
       </c>
       <c r="Z3" t="b">
         <v>1</v>
@@ -1072,7 +1054,7 @@
         <v>2.8</v>
       </c>
       <c r="AH3">
-        <v>7.34</v>
+        <v>4.41</v>
       </c>
       <c r="AI3" t="b">
         <v>0</v>
@@ -1158,19 +1140,19 @@
         <v>88.9</v>
       </c>
       <c r="O4">
-        <v>0.108</v>
+        <v>1.425</v>
       </c>
       <c r="P4">
-        <v>100</v>
+        <v>67.7</v>
       </c>
       <c r="Q4">
-        <v>9.0299999999999994</v>
+        <v>33.82</v>
       </c>
       <c r="R4">
         <v>70</v>
       </c>
       <c r="S4">
-        <v>7.7510000000000003</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="T4" t="b">
         <v>1</v>
@@ -1182,13 +1164,13 @@
         <v>1.7</v>
       </c>
       <c r="W4">
-        <v>323</v>
+        <v>66.2</v>
       </c>
       <c r="X4">
         <v>2638.3</v>
       </c>
       <c r="Y4">
-        <v>0.122</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="Z4" t="b">
         <v>1</v>
@@ -1215,7 +1197,7 @@
         <v>2.85</v>
       </c>
       <c r="AH4">
-        <v>7.52</v>
+        <v>4.53</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -1277,13 +1259,13 @@
         <v>3.3499999999985408</v>
       </c>
       <c r="G5">
-        <v>3.3</v>
+        <v>5.25</v>
       </c>
       <c r="H5">
-        <v>5.8</v>
+        <v>3.65</v>
       </c>
       <c r="I5">
-        <v>19.14</v>
+        <v>19.161999999999999</v>
       </c>
       <c r="J5">
         <v>1.2</v>
@@ -1295,43 +1277,43 @@
         <v>80</v>
       </c>
       <c r="M5">
-        <v>169.9</v>
+        <v>170</v>
       </c>
       <c r="N5">
         <v>2.2000000000000002</v>
       </c>
       <c r="O5">
-        <v>1.2999999999999999E-2</v>
+        <v>2.5249999999999999</v>
       </c>
       <c r="P5">
-        <v>100</v>
+        <v>67.2</v>
       </c>
       <c r="Q5">
-        <v>8.99</v>
+        <v>34.67</v>
       </c>
       <c r="R5">
         <v>70</v>
       </c>
       <c r="S5">
-        <v>7.7839999999999998</v>
+        <v>2.0190000000000001</v>
       </c>
       <c r="T5" t="b">
         <v>1</v>
       </c>
       <c r="U5">
-        <v>3.1</v>
+        <v>5.05</v>
       </c>
       <c r="V5">
-        <v>1.95</v>
+        <v>3.9</v>
       </c>
       <c r="W5">
-        <v>69.7</v>
+        <v>73.5</v>
       </c>
       <c r="X5">
-        <v>500.9</v>
+        <v>315.2</v>
       </c>
       <c r="Y5">
-        <v>0.13900000000000001</v>
+        <v>0.23300000000000001</v>
       </c>
       <c r="Z5" t="b">
         <v>1</v>
@@ -1346,7 +1328,7 @@
         <v>42.1</v>
       </c>
       <c r="AD5">
-        <v>1.5069999999999999</v>
+        <v>1.5089999999999999</v>
       </c>
       <c r="AE5" t="b">
         <v>1</v>
@@ -1355,10 +1337,10 @@
         <v>82</v>
       </c>
       <c r="AG5">
-        <v>3.1</v>
+        <v>5.05</v>
       </c>
       <c r="AH5">
-        <v>8.82</v>
+        <v>15.98</v>
       </c>
       <c r="AI5" t="b">
         <v>1</v>
@@ -1373,7 +1355,7 @@
         <v>87</v>
       </c>
       <c r="AM5">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="AN5" t="s">
         <v>89</v>
@@ -1408,7 +1390,7 @@
         <v>77</v>
       </c>
       <c r="C6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6">
         <v>0.2</v>
